--- a/Zara_Khan_Optimized_Calendar.xlsx
+++ b/Zara_Khan_Optimized_Calendar.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5265,6 +5265,80 @@
         <v>115</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DAY101_POST_01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Day 101</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Feed Photo</t>
+        </is>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Zara Khan quiet morning aesthetic in sunlit South Mumbai heritage cafe patio reading book with coffee</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Natural warm morning light streaming through vintage wooden blinds, ivory linen button-up shirt, layered delicate gold necklaces, relaxed candid smile, 35mm film aesthetic, Zara Khan avatar reference consistency</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The quietest hours of Bombay are always the most poetic. Linen mornings and black coffee.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Acoustic lo-fi warm morning guitar chords</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://in.pinterest.com/pin/1105985746020500854/</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1IaeGtZF6cLdXTyREF6HiDwyY3x9_0sOf</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ZARA_KHAN.png</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Zara_Khan_Optimized_Calendar.xlsx
+++ b/Zara_Khan_Optimized_Calendar.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,6 +167,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5289,12 +5290,11 @@
       <c r="E74" t="b">
         <v>1</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>GENERATED</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Zara Khan quiet morning aesthetic in sunlit South Mumbai heritage cafe patio reading book with coffee</t>
@@ -5317,14 +5317,29 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://in.pinterest.com/pin/1105985746020500854/</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+          <t>https://images.unsplash.com/photo-1554118811-1e0d58224f24?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>references/DAY101_POST_01.jpg</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Cinematic 35mm film photography of Zara Khan in a quiet sunlit South Mumbai heritage cafe patio. She has long dark natural wavy hair, expressive warm brown eyes, and a relaxed candid smile. She is wearing an ivory linen button-up shirt and layered delicate gold necklaces, holding a coffee cup and reading a book. Natural warm morning light streams through vintage wooden blinds casting soft shadows. Photorealistic textures, soft depth of field, authentic candid lifestyle influencer aesthetic, Fujifilm color grade.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>plastic skin, artificial lighting, CGI, 3D render, modern minimalist sterile aesthetic, heavy makeup, distorted anatomy, blurry, oversaturated colors</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>outputs/DAY101_POST_01.png</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr">
         <is>
           <t>https://drive.google.com/drive/folders/1IaeGtZF6cLdXTyREF6HiDwyY3x9_0sOf</t>
@@ -5332,7 +5347,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>ZARA_KHAN.png</t>
+          <t>https://images.unsplash.com/photo-1583391733956-3750e0ff4e8b?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
         </is>
       </c>
       <c r="T74" t="n">

--- a/Zara_Khan_Optimized_Calendar.xlsx
+++ b/Zara_Khan_Optimized_Calendar.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5354,6 +5354,157 @@
         <v>184</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DAY102_POST_01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Day 102</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Feed Photo</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Zara Khan quiet luxury evening aesthetic in modern Fort art gallery admiring contemporary paintings</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Modern art gallery white walls with framed artworks and reflective polished floors, deep royal purple silk saree with intricate gold zari border, sleeveless black velvet blouse, gold jhumkas, serene poise, Zara Khan face lock consistency</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Art speaks loudest in the quiet spaces between galleries. An evening surrounded by perspective in Fort.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Contemporary ambient gallery cello and acoustic strings</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1518998053901-5348d3961a04?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>references/DAY102_POST_01.jpg</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1IaeGtZF6cLdXTyREF6HiDwyY3x9_0sOf</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1610030469983-98e550d6193c?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DAY103_POST_01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Day 103</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Feed Photo</t>
+        </is>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Zara Khan heritage library study aesthetic in warm mahogany lounge with antique bookshelves and soft lamp glow</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Rich mahogany wood-paneled study with warm pleated lampshades and antique books, vibrant crimson rose and gold Kanjeevaram silk saree with bold zari borders, traditional gold temple jewelry, serene poised smile, Zara Khan face lock consistency</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Surrounded by centuries of stories in the quiet heart of Bombay. Crimson silks and warm lamplight.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Traditional sitar and warm classical Indian acoustic melody</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1590381105924-c72589b9ef3f?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>references/DAY103_POST_01.jpg</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1IaeGtZF6cLdXTyREF6HiDwyY3x9_0sOf</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>https://images.unsplash.com/photo-1617627143750-d86bc21e42bb?auto=format&amp;fit=crop&amp;w=1080&amp;q=80</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
